--- a/Step3-ReuseTestCase/data-final/test_case_info.xlsx
+++ b/Step3-ReuseTestCase/data-final/test_case_info.xlsx
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P32" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P36" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P39" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P43" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P49" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P51" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P55" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P56" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P58" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P60" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P62" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P63" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P67" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -5519,10 +5519,10 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P68" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P69" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P70" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P71" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P74" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P75" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P82" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -6657,10 +6657,10 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P85" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P86" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P90" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P93" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -7591,10 +7591,10 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P96" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="M99" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P99" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="M101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P101" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="M103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="M104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P104" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P105" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="M106" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -8355,10 +8355,10 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P106" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="M111" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -8693,10 +8693,10 @@
         </is>
       </c>
       <c r="O111" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P111" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="M112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P112" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         </is>
       </c>
       <c r="M115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
@@ -8974,10 +8974,10 @@
         </is>
       </c>
       <c r="O115" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P115" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         </is>
       </c>
       <c r="M117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N117" t="inlineStr">
         <is>
@@ -9126,10 +9126,10 @@
         </is>
       </c>
       <c r="O117" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P117" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="M120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P120" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="M122" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P122" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="M125" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
@@ -9730,10 +9730,10 @@
         </is>
       </c>
       <c r="O125" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P125" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="M129" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="O129" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P129" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="M130" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P130" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="M132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
@@ -10268,10 +10268,10 @@
         </is>
       </c>
       <c r="O132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P132" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         </is>
       </c>
       <c r="M133" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="O133" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P133" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N134" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="M135" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="O135" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P135" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         </is>
       </c>
       <c r="M136" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P136" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         </is>
       </c>
       <c r="M141" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
@@ -10942,10 +10942,10 @@
         </is>
       </c>
       <c r="O141" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P141" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         </is>
       </c>
       <c r="M142" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N142" t="inlineStr">
         <is>
@@ -11016,10 +11016,10 @@
         </is>
       </c>
       <c r="O142" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P142" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         </is>
       </c>
       <c r="M145" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
@@ -11242,10 +11242,10 @@
         </is>
       </c>
       <c r="O145" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P145" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         </is>
       </c>
       <c r="M147" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="O147" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P147" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         </is>
       </c>
       <c r="M149" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N149" t="inlineStr">
         <is>
@@ -11542,10 +11542,10 @@
         </is>
       </c>
       <c r="O149" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P149" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N150" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>0</v>
       </c>
       <c r="P150" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N152" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>0</v>
       </c>
       <c r="P153" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         </is>
       </c>
       <c r="M154" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N154" t="inlineStr">
         <is>
@@ -11900,10 +11900,10 @@
         </is>
       </c>
       <c r="O154" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P154" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         </is>
       </c>
       <c r="M155" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
@@ -11982,10 +11982,10 @@
         </is>
       </c>
       <c r="O155" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P155" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>0</v>
       </c>
       <c r="P156" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N157" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="M158" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="O158" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P158" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N159" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>0</v>
       </c>
       <c r="P159" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         </is>
       </c>
       <c r="M160" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N160" t="inlineStr">
         <is>
@@ -12344,10 +12344,10 @@
         </is>
       </c>
       <c r="O160" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P160" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         </is>
       </c>
       <c r="M161" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N161" t="inlineStr">
         <is>
@@ -12426,10 +12426,10 @@
         </is>
       </c>
       <c r="O161" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P161" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         </is>
       </c>
       <c r="M162" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N162" t="inlineStr">
         <is>
@@ -12508,10 +12508,10 @@
         </is>
       </c>
       <c r="O162" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P162" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="M163" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N163" t="inlineStr">
         <is>
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="O163" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P163" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         </is>
       </c>
       <c r="M164" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N164" t="inlineStr">
         <is>
@@ -12660,10 +12660,10 @@
         </is>
       </c>
       <c r="O164" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P164" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N165" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>0</v>
       </c>
       <c r="P165" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>0</v>
       </c>
       <c r="P166" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="M167" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N167" t="inlineStr">
         <is>
@@ -12886,10 +12886,10 @@
         </is>
       </c>
       <c r="O167" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P167" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="M168" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
@@ -12968,10 +12968,10 @@
         </is>
       </c>
       <c r="O168" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P168" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         </is>
       </c>
       <c r="M169" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N169" t="inlineStr">
         <is>
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="O169" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P169" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         </is>
       </c>
       <c r="M170" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
@@ -13120,10 +13120,10 @@
         </is>
       </c>
       <c r="O170" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P170" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         </is>
       </c>
       <c r="M171" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N171" t="inlineStr">
         <is>
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="O171" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P171" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         </is>
       </c>
       <c r="M172" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N172" t="inlineStr">
         <is>
@@ -13284,10 +13284,10 @@
         </is>
       </c>
       <c r="O172" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P172" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>0</v>
       </c>
       <c r="P173" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N174" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>0</v>
       </c>
       <c r="P174" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N175" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>0</v>
       </c>
       <c r="P175" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         </is>
       </c>
       <c r="M176" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N176" t="inlineStr">
         <is>
@@ -13588,10 +13588,10 @@
         </is>
       </c>
       <c r="O176" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P176" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         </is>
       </c>
       <c r="M177" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
@@ -13670,10 +13670,10 @@
         </is>
       </c>
       <c r="O177" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P177" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         </is>
       </c>
       <c r="M178" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
@@ -13740,10 +13740,10 @@
         </is>
       </c>
       <c r="O178" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P178" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>0</v>
       </c>
       <c r="P179" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N180" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>0</v>
       </c>
       <c r="P180" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         </is>
       </c>
       <c r="M181" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N181" t="inlineStr">
         <is>
@@ -13970,10 +13970,10 @@
         </is>
       </c>
       <c r="O181" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P181" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         </is>
       </c>
       <c r="M182" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N182" t="inlineStr">
         <is>
@@ -14052,10 +14052,10 @@
         </is>
       </c>
       <c r="O182" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P182" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>0</v>
       </c>
       <c r="P183" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         </is>
       </c>
       <c r="M186" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N186" t="inlineStr">
         <is>
@@ -14332,10 +14332,10 @@
         </is>
       </c>
       <c r="O186" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P186" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         </is>
       </c>
       <c r="M189" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N189" t="inlineStr">
         <is>
@@ -14542,10 +14542,10 @@
         </is>
       </c>
       <c r="O189" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P189" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         </is>
       </c>
       <c r="M190" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N190" t="inlineStr">
         <is>
@@ -14612,10 +14612,10 @@
         </is>
       </c>
       <c r="O190" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P190" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         </is>
       </c>
       <c r="M191" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
@@ -14690,10 +14690,10 @@
         </is>
       </c>
       <c r="O191" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P191" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N193" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>0</v>
       </c>
       <c r="P193" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N194" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>0</v>
       </c>
       <c r="P194" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="M195" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
@@ -14982,10 +14982,10 @@
         </is>
       </c>
       <c r="O195" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P195" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N196" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>0</v>
       </c>
       <c r="P196" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         </is>
       </c>
       <c r="M198" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N198" t="inlineStr">
         <is>
@@ -15196,10 +15196,10 @@
         </is>
       </c>
       <c r="O198" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P198" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M199" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N199" t="inlineStr">
         <is>
@@ -15278,10 +15278,10 @@
         </is>
       </c>
       <c r="O199" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P199" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N200" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>0</v>
       </c>
       <c r="P200" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>0</v>
       </c>
       <c r="P201" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N202" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>0</v>
       </c>
       <c r="P202" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N203" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>0</v>
       </c>
       <c r="P203" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N204" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>0</v>
       </c>
       <c r="P204" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N205" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>0</v>
       </c>
       <c r="P205" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         </is>
       </c>
       <c r="M206" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N206" t="inlineStr">
         <is>
@@ -15788,10 +15788,10 @@
         </is>
       </c>
       <c r="O206" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P206" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         </is>
       </c>
       <c r="M208" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N208" t="inlineStr">
         <is>
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="O208" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P208" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N209" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>0</v>
       </c>
       <c r="P209" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N211" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>0</v>
       </c>
       <c r="P211" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N212" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>0</v>
       </c>
       <c r="P212" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         </is>
       </c>
       <c r="M214" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N214" t="inlineStr">
         <is>
@@ -16324,10 +16324,10 @@
         </is>
       </c>
       <c r="O214" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P214" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         </is>
       </c>
       <c r="M215" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
@@ -16406,10 +16406,10 @@
         </is>
       </c>
       <c r="O215" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P215" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         </is>
       </c>
       <c r="M216" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N216" t="inlineStr">
         <is>
@@ -16488,10 +16488,10 @@
         </is>
       </c>
       <c r="O216" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P216" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         </is>
       </c>
       <c r="M217" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N217" t="inlineStr">
         <is>
@@ -16570,10 +16570,10 @@
         </is>
       </c>
       <c r="O217" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P217" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         </is>
       </c>
       <c r="M218" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N218" t="inlineStr">
         <is>
@@ -16652,10 +16652,10 @@
         </is>
       </c>
       <c r="O218" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P218" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         </is>
       </c>
       <c r="M219" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N219" t="inlineStr">
         <is>
@@ -16726,10 +16726,10 @@
         </is>
       </c>
       <c r="O219" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P219" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         </is>
       </c>
       <c r="M220" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N220" t="inlineStr">
         <is>
@@ -16808,10 +16808,10 @@
         </is>
       </c>
       <c r="O220" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P220" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N222" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>0</v>
       </c>
       <c r="P222" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N225" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>0</v>
       </c>
       <c r="P225" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
       <c r="M227" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N227" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>0</v>
       </c>
       <c r="P227" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N229" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>0</v>
       </c>
       <c r="P229" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>0</v>
       </c>
       <c r="P230" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         </is>
       </c>
       <c r="M231" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
@@ -17558,10 +17558,10 @@
         </is>
       </c>
       <c r="O231" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P231" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         </is>
       </c>
       <c r="M232" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N232" t="inlineStr">
         <is>
@@ -17640,10 +17640,10 @@
         </is>
       </c>
       <c r="O232" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P232" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>0</v>
       </c>
       <c r="P234" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         </is>
       </c>
       <c r="M236" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N236" t="inlineStr">
         <is>
@@ -17920,10 +17920,10 @@
         </is>
       </c>
       <c r="O236" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P236" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         </is>
       </c>
       <c r="M237" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N237" t="inlineStr">
         <is>
@@ -18002,10 +18002,10 @@
         </is>
       </c>
       <c r="O237" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P237" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
@@ -18084,10 +18084,10 @@
         </is>
       </c>
       <c r="O238" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P238" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr"/>
       <c r="M239" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>0</v>
       </c>
       <c r="P239" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         </is>
       </c>
       <c r="M240" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -18224,10 +18224,10 @@
         </is>
       </c>
       <c r="O240" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P240" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N242" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>0</v>
       </c>
       <c r="P242" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr"/>
       <c r="M244" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N244" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>0</v>
       </c>
       <c r="P244" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N245" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>0</v>
       </c>
       <c r="P245" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         </is>
       </c>
       <c r="M246" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N246" t="inlineStr">
         <is>
@@ -18664,10 +18664,10 @@
         </is>
       </c>
       <c r="O246" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P246" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -18730,7 +18730,7 @@
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
       <c r="M247" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N247" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>0</v>
       </c>
       <c r="P247" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         </is>
       </c>
       <c r="M250" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N250" t="inlineStr">
         <is>
@@ -18948,10 +18948,10 @@
         </is>
       </c>
       <c r="O250" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P250" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         </is>
       </c>
       <c r="M251" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N251" t="inlineStr">
         <is>
@@ -19010,10 +19010,10 @@
         </is>
       </c>
       <c r="O251" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P251" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         </is>
       </c>
       <c r="M252" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N252" t="inlineStr">
         <is>
@@ -19088,10 +19088,10 @@
         </is>
       </c>
       <c r="O252" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P252" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N253" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>0</v>
       </c>
       <c r="P253" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="M254" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N254" t="inlineStr">
         <is>
@@ -19236,10 +19236,10 @@
         </is>
       </c>
       <c r="O254" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P254" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         </is>
       </c>
       <c r="M256" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N256" t="inlineStr">
         <is>
@@ -19376,10 +19376,10 @@
         </is>
       </c>
       <c r="O256" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P256" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         </is>
       </c>
       <c r="M259" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N259" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>10</v>
       </c>
       <c r="P259" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         </is>
       </c>
       <c r="M260" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N260" t="inlineStr">
         <is>
@@ -19676,10 +19676,10 @@
         </is>
       </c>
       <c r="O260" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P260" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr"/>
       <c r="M261" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N261" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>0</v>
       </c>
       <c r="P261" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="M262" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N262" t="inlineStr">
         <is>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="O262" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P262" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
       <c r="M264" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N264" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>0</v>
       </c>
       <c r="P264" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         </is>
       </c>
       <c r="M266" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N266" t="inlineStr">
         <is>
@@ -20128,10 +20128,10 @@
         </is>
       </c>
       <c r="O266" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P266" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         </is>
       </c>
       <c r="M267" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N267" t="inlineStr">
         <is>
@@ -20210,10 +20210,10 @@
         </is>
       </c>
       <c r="O267" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P267" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
       <c r="M268" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N268" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>0</v>
       </c>
       <c r="P268" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
